--- a/Result/profitability/3205.xlsx
+++ b/Result/profitability/3205.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.36</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.26625</v>
+        <v>-0.2125</v>
       </c>
       <c r="N2" t="n">
-        <v>17.59125</v>
+        <v>16.19625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.18</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2325</v>
+        <v>-0.20375</v>
       </c>
       <c r="N3" t="n">
-        <v>15.37875</v>
+        <v>13.52125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.25</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2325</v>
+        <v>-0.175</v>
       </c>
       <c r="N4" t="n">
-        <v>14.8225</v>
+        <v>13.21</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.37</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.21875</v>
+        <v>-0.18</v>
       </c>
       <c r="N5" t="n">
-        <v>8.36875</v>
+        <v>6.72625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>-0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.19875</v>
+        <v>-0.18875</v>
       </c>
       <c r="N6" t="n">
-        <v>12.14125</v>
+        <v>10.905</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>-0.18</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.20875</v>
+        <v>-0.185</v>
       </c>
       <c r="N7" t="n">
-        <v>12.50625</v>
+        <v>11.20375</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.32</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2225</v>
+        <v>-0.23125</v>
       </c>
       <c r="N8" t="n">
-        <v>13.8075</v>
+        <v>13.2625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>-1.08</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.445</v>
+        <v>-0.4450000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>28.99625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>188</v>
+      </c>
+      <c r="D75" t="n">
+        <v>179</v>
+      </c>
+      <c r="E75" t="n">
+        <v>9</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-3.31%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.22375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.38125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4765027322404372</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.9393939393939394</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-13.14</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.7328499721137758</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
